--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.425633411</v>
+        <v>320074.8015362156</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>2995243.613506389</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20355670.24425592</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818937</v>
+        <v>4812058.02286789</v>
       </c>
     </row>
     <row r="11">
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>11.94928935461252</v>
@@ -1165,28 +1165,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6263639150735023</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1205,22 +1205,22 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J9" t="n">
         <v>0.7465913262578567</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.27419204266741</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>23.19571111787229</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1402,19 +1402,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1484,16 +1484,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U12" t="n">
-        <v>22.15420867374214</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>23.55275130756091</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,13 +1560,13 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1606,19 +1606,19 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1639,19 +1639,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1685,19 +1685,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1767,19 +1767,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,16 +1794,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1843,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>12.71311064538747</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1876,19 +1876,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1958,25 +1958,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>19.72731862540289</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2046,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>22.02246762618611</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="20">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>202.2821007854552</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2125,19 +2125,19 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>123.3365499318636</v>
       </c>
       <c r="U21" t="n">
         <v>225.9413820809748</v>
@@ -2210,10 +2210,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>35.36610207477823</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>22.0339917726843</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2384,31 +2384,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>118.5540130169416</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>24.0757291863596</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2484,55 +2484,55 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2599,19 +2599,19 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2621,22 +2621,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78.85776412257762</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>146.9102640950556</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2669,19 +2669,19 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -2700,70 +2700,70 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2836,19 +2836,19 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>212.2728</v>
+        <v>212.285385643442</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>81.94696239689883</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2912,19 +2912,19 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
-        <v>104.3149513424282</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
         <v>205.6826957773044</v>
@@ -2979,13 +2979,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>130.4655268502615</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3031,13 +3031,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3064,28 +3064,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>40.01622368765416</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>179.7283339446665</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="33">
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>8.886618849664252</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3143,28 +3143,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>32.52410020134062</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3174,13 +3174,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3307,16 +3307,16 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="U35" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3332,16 +3332,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>22.83881635013257</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3383,22 +3383,22 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>95.60580665331359</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3462,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>29.85921600351671</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>162.5393852224019</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3584,16 +3584,16 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>44.34825113042956</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3617,22 +3617,22 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3727,16 +3727,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3775,16 +3775,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>27.7505828443055</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>182.3975862107084</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3809,28 +3809,28 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>60.57055442525026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>22.92687081970527</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3939,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="C8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="D8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="E8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="F8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="G8" t="n">
-        <v>66.67524177233588</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="H8" t="n">
-        <v>40.41261550970962</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="I8" t="n">
-        <v>14.14998924708335</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L8" t="n">
-        <v>52.52000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M8" t="n">
-        <v>52.52000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="V8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="W8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="X8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="Y8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.11961254265382</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L9" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M9" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="N9" t="n">
-        <v>52.52000000000001</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P9" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="C10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="D10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="E10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="F10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="G10" t="n">
-        <v>103.3623149756393</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="H10" t="n">
-        <v>77.09968871301299</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="I10" t="n">
-        <v>50.83706245038672</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>103.6392766348993</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="S10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="T10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="U10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="V10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="W10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="X10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="Y10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F11" t="n">
-        <v>92.93786803496215</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G11" t="n">
-        <v>66.67524177233588</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H11" t="n">
-        <v>40.41261550970962</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M11" t="n">
-        <v>53.56</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N11" t="n">
-        <v>79.3</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="C12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="D12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="E12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="F12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="G12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="H12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M12" t="n">
-        <v>2.08</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N12" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O12" t="n">
-        <v>52.52000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S12" t="n">
-        <v>51.47474747474747</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T12" t="n">
-        <v>25.2121212121212</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="V12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="W12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="X12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="C13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="D13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="E13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="F13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="G13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="H13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="I13" t="n">
-        <v>51.19778581548745</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093952</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>101.2510699645389</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.98844370191262</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R13" t="n">
-        <v>74.98844370191262</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="U13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="V13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="W13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="X13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="Y13" t="n">
-        <v>74.98844370191262</v>
+        <v>22.09498869872634</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F14" t="n">
-        <v>92.93786803496215</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G14" t="n">
-        <v>66.67524177233588</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H14" t="n">
-        <v>40.41261550970962</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I14" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L14" t="n">
-        <v>52.52000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M14" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F15" t="n">
-        <v>81.62201144066449</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G15" t="n">
-        <v>55.35938517803824</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H15" t="n">
-        <v>29.09675891541198</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M15" t="n">
-        <v>26.78000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O15" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F17" t="n">
-        <v>99.15847409556821</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G17" t="n">
-        <v>70.87564581273992</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H17" t="n">
-        <v>42.59281752991163</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I17" t="n">
-        <v>14.30998924708335</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>29.96</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M17" t="n">
-        <v>57.68</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N17" t="n">
-        <v>85.40000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>44.53106090472204</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>29.96</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>29.96</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>56.56</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O18" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>55.43434343434343</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>27.15151515151514</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="U18" t="n">
-        <v>27.15151515151514</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="V18" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>50.00249887508694</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>22.13378649092923</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>22.13378649092923</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>22.13378649092923</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>105.7399236434024</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="T19" t="n">
-        <v>109.3334016426122</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="U19" t="n">
-        <v>81.05057335978395</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="V19" t="n">
-        <v>52.76774507695567</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="W19" t="n">
-        <v>24.48491679412739</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>50.00249887508694</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="C20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>710.4740411974295</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>710.4740411974295</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>467.0396977630861</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X20" t="n">
-        <v>467.0396977630861</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y20" t="n">
-        <v>223.6053543287427</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>851.7806659261865</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O21" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>761.813405358766</v>
+        <v>839.4747818420872</v>
       </c>
       <c r="U21" t="n">
-        <v>533.5897870951551</v>
+        <v>611.2511635784762</v>
       </c>
       <c r="V21" t="n">
-        <v>298.4376788634124</v>
+        <v>376.0990553467335</v>
       </c>
       <c r="W21" t="n">
-        <v>55.00333542906893</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="X21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="C22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="D22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="E22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="F22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="G22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R22" t="n">
-        <v>964</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="S22" t="n">
-        <v>964</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="T22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="U22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="V22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="W22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="X22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="Y22" t="n">
-        <v>829.4677095097293</v>
+        <v>41.77557929797318</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>477.1313131313132</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C23" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D23" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y23" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>419.918063556189</v>
+        <v>844.3056272106952</v>
       </c>
       <c r="C24" t="n">
-        <v>419.918063556189</v>
+        <v>669.8525979295682</v>
       </c>
       <c r="D24" t="n">
-        <v>419.918063556189</v>
+        <v>520.918188268317</v>
       </c>
       <c r="E24" t="n">
-        <v>395.5991451861288</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="F24" t="n">
-        <v>249.0645872130137</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G24" t="n">
-        <v>110.3337617956292</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H24" t="n">
-        <v>110.3337617956292</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>486.8199999999999</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N24" t="n">
-        <v>725.41</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V24" t="n">
-        <v>627.6783623211429</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W24" t="n">
-        <v>627.6783623211429</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X24" t="n">
-        <v>627.6783623211429</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y24" t="n">
-        <v>419.918063556189</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C26" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D26" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E26" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>233.6969696969697</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y26" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>649.1935845737345</v>
+        <v>452.9407326573341</v>
       </c>
       <c r="C27" t="n">
-        <v>474.7405552926075</v>
+        <v>452.9407326573341</v>
       </c>
       <c r="D27" t="n">
-        <v>325.8061456313562</v>
+        <v>452.9407326573341</v>
       </c>
       <c r="E27" t="n">
-        <v>166.5686906259007</v>
+        <v>304.5465265007123</v>
       </c>
       <c r="F27" t="n">
-        <v>20.03413265278571</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M27" t="n">
-        <v>613.1906659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N27" t="n">
-        <v>781.3565223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="V27" t="n">
-        <v>728.8478917682573</v>
+        <v>660.701031422288</v>
       </c>
       <c r="W27" t="n">
-        <v>728.8478917682573</v>
+        <v>660.701031422288</v>
       </c>
       <c r="X27" t="n">
-        <v>728.8478917682573</v>
+        <v>660.701031422288</v>
       </c>
       <c r="Y27" t="n">
-        <v>728.8478917682573</v>
+        <v>452.9407326573341</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V29" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W29" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.28</v>
+        <v>102.8099852548154</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>102.8099852548154</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>102.8099852548154</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>102.8099852548154</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>102.8099852548154</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>102.8099852548154</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>102.8099852548154</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>234.7819638733197</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N30" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U30" t="n">
-        <v>735.7763817363891</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V30" t="n">
-        <v>500.6242735046464</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W30" t="n">
-        <v>500.6242735046464</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="X30" t="n">
-        <v>395.2556357850219</v>
+        <v>310.5702840197694</v>
       </c>
       <c r="Y30" t="n">
-        <v>187.495337020068</v>
+        <v>102.8099852548154</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>446.9736258286929</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="C32" t="n">
-        <v>446.9736258286929</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="D32" t="n">
-        <v>446.9736258286929</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E32" t="n">
-        <v>446.9736258286929</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F32" t="n">
-        <v>446.9736258286929</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G32" t="n">
-        <v>229.8019086569757</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H32" t="n">
-        <v>229.8019086569757</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>22.36462077340309</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R32" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S32" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T32" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U32" t="n">
-        <v>446.9736258286929</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="V32" t="n">
-        <v>446.9736258286929</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="W32" t="n">
-        <v>446.9736258286929</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="X32" t="n">
-        <v>446.9736258286929</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="Y32" t="n">
-        <v>446.9736258286929</v>
+        <v>234.8012144439637</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
       <c r="C33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
       <c r="D33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
       <c r="E33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
       <c r="F33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L33" t="n">
-        <v>221.45</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="M33" t="n">
-        <v>434.3</v>
+        <v>183.0578391930369</v>
       </c>
       <c r="N33" t="n">
-        <v>647.15</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="O33" t="n">
-        <v>860</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>827.1473735339994</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S33" t="n">
-        <v>653.7300289846683</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T33" t="n">
-        <v>451.5434343434343</v>
+        <v>659.389396090879</v>
       </c>
       <c r="U33" t="n">
-        <v>234.3717171717172</v>
+        <v>659.389396090879</v>
       </c>
       <c r="V33" t="n">
-        <v>234.3717171717172</v>
+        <v>659.389396090879</v>
       </c>
       <c r="W33" t="n">
-        <v>17.2</v>
+        <v>441.8197014615575</v>
       </c>
       <c r="X33" t="n">
-        <v>17.2</v>
+        <v>233.9682012560247</v>
       </c>
       <c r="Y33" t="n">
-        <v>17.2</v>
+        <v>26.2079024910708</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="C34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="D34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="E34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="F34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="G34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="H34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="I34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="J34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="K34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L34" t="n">
-        <v>752.7818345174422</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M34" t="n">
-        <v>791.9698727096644</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N34" t="n">
-        <v>835.6607233651007</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D35" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L35" t="n">
-        <v>292.1005276501127</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M35" t="n">
-        <v>504.9505276501126</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N35" t="n">
-        <v>710.8050498573519</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T35" t="n">
-        <v>849.9083846317729</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="U35" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="V35" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="W35" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="X35" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="Y35" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.26951146478038</v>
+        <v>166.1659294758935</v>
       </c>
       <c r="C36" t="n">
-        <v>40.26951146478038</v>
+        <v>166.1659294758935</v>
       </c>
       <c r="D36" t="n">
-        <v>40.26951146478038</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>251.6565223866492</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M36" t="n">
-        <v>251.6565223866492</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N36" t="n">
-        <v>464.5065223866492</v>
+        <v>782.3092529910735</v>
       </c>
       <c r="O36" t="n">
-        <v>677.3565223866492</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="U36" t="n">
-        <v>642.8282828282828</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="V36" t="n">
-        <v>425.6565656565656</v>
+        <v>591.5871243107479</v>
       </c>
       <c r="W36" t="n">
-        <v>208.4848484848484</v>
+        <v>374.0174296814264</v>
       </c>
       <c r="X36" t="n">
-        <v>208.4848484848484</v>
+        <v>166.1659294758935</v>
       </c>
       <c r="Y36" t="n">
-        <v>208.4848484848484</v>
+        <v>166.1659294758935</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="T37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>415.5649502883385</v>
+        <v>264.9620386899402</v>
       </c>
       <c r="C38" t="n">
-        <v>415.5649502883385</v>
+        <v>47.39234406061874</v>
       </c>
       <c r="D38" t="n">
-        <v>198.3932331166214</v>
+        <v>47.39234406061874</v>
       </c>
       <c r="E38" t="n">
-        <v>17.2</v>
+        <v>47.39234406061874</v>
       </c>
       <c r="F38" t="n">
-        <v>17.2</v>
+        <v>47.39234406061874</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>47.39234406061874</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>47.39234406061874</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="S38" t="n">
-        <v>849.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="T38" t="n">
-        <v>849.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="U38" t="n">
-        <v>849.9083846317729</v>
+        <v>482.5317333192617</v>
       </c>
       <c r="V38" t="n">
-        <v>849.9083846317729</v>
+        <v>482.5317333192617</v>
       </c>
       <c r="W38" t="n">
-        <v>849.9083846317729</v>
+        <v>482.5317333192617</v>
       </c>
       <c r="X38" t="n">
-        <v>849.9083846317729</v>
+        <v>482.5317333192617</v>
       </c>
       <c r="Y38" t="n">
-        <v>632.7366674600557</v>
+        <v>482.5317333192617</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>425.6565656565656</v>
+        <v>340.6501720144431</v>
       </c>
       <c r="C39" t="n">
-        <v>425.6565656565656</v>
+        <v>176.4689748200978</v>
       </c>
       <c r="D39" t="n">
-        <v>425.6565656565656</v>
+        <v>176.4689748200978</v>
       </c>
       <c r="E39" t="n">
-        <v>266.4191106511101</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>266.4191106511101</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>221.6228973880499</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>108.2537617956292</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.95413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>17.2</v>
+        <v>252.4523977063661</v>
       </c>
       <c r="M39" t="n">
-        <v>230.05</v>
+        <v>252.4523977063661</v>
       </c>
       <c r="N39" t="n">
-        <v>395.1119638733197</v>
+        <v>465.6924554125641</v>
       </c>
       <c r="O39" t="n">
-        <v>607.9619638733197</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="T39" t="n">
-        <v>860</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="U39" t="n">
-        <v>642.8282828282828</v>
+        <v>340.6501720144431</v>
       </c>
       <c r="V39" t="n">
-        <v>642.8282828282828</v>
+        <v>340.6501720144431</v>
       </c>
       <c r="W39" t="n">
-        <v>425.6565656565656</v>
+        <v>340.6501720144431</v>
       </c>
       <c r="X39" t="n">
-        <v>425.6565656565656</v>
+        <v>340.6501720144431</v>
       </c>
       <c r="Y39" t="n">
-        <v>425.6565656565656</v>
+        <v>340.6501720144431</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>447.3430303030303</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="C41" t="n">
-        <v>232.1915151515151</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="D41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>196.4204723580617</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="R41" t="n">
-        <v>690.5254372164702</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="S41" t="n">
-        <v>690.5254372164702</v>
+        <v>632.4740556806947</v>
       </c>
       <c r="T41" t="n">
-        <v>662.4945454545455</v>
+        <v>416.8939914207524</v>
       </c>
       <c r="U41" t="n">
-        <v>662.4945454545455</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="V41" t="n">
-        <v>662.4945454545455</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="W41" t="n">
-        <v>662.4945454545455</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="X41" t="n">
-        <v>662.4945454545455</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="Y41" t="n">
-        <v>662.4945454545455</v>
+        <v>232.6540053493298</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>636.8484848484849</v>
+        <v>191.5269703705144</v>
       </c>
       <c r="C42" t="n">
-        <v>636.8484848484849</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D42" t="n">
-        <v>575.6661066411614</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E42" t="n">
-        <v>416.4286516357059</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>269.8940936625909</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>131.1632682452064</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>227.91</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="M42" t="n">
-        <v>438.78</v>
+        <v>179.0789763803525</v>
       </c>
       <c r="N42" t="n">
-        <v>649.65</v>
+        <v>390.368997361522</v>
       </c>
       <c r="O42" t="n">
-        <v>669.3565223866492</v>
+        <v>601.6590183426915</v>
       </c>
       <c r="P42" t="n">
-        <v>852</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>830.538599095932</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>830.538599095932</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>830.538599095932</v>
       </c>
       <c r="U42" t="n">
-        <v>852</v>
+        <v>614.9585348359897</v>
       </c>
       <c r="V42" t="n">
-        <v>852</v>
+        <v>614.9585348359897</v>
       </c>
       <c r="W42" t="n">
-        <v>636.8484848484849</v>
+        <v>399.3784705760473</v>
       </c>
       <c r="X42" t="n">
-        <v>636.8484848484849</v>
+        <v>191.5269703705144</v>
       </c>
       <c r="Y42" t="n">
-        <v>636.8484848484849</v>
+        <v>191.5269703705144</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>744.7818345174422</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>783.9698727096644</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>827.6607233651007</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>852</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="U43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="V43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="W43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>260.7159099194822</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O8" t="n">
-        <v>230.0982114216867</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8515,22 +8515,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>163.5038747293692</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>157.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P9" t="n">
-        <v>159.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,19 +8670,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M11" t="n">
-        <v>256.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O11" t="n">
-        <v>255.0477063711817</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
         <v>231.2329957552695</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>159.9744074143302</v>
+        <v>158.5595353283699</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>245.0393459944755</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>230.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N14" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>256.9668982903736</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,22 +9223,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>165.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869682</v>
       </c>
       <c r="N18" t="n">
-        <v>158.2103989520202</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>161.5644326746464</v>
       </c>
       <c r="Q18" t="n">
         <v>139.9817740860215</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,13 +9466,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>185.8535934954385</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P21" t="n">
         <v>133.9744074143302</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>382.1106946610595</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P24" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9937,22 +9937,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>233.2169876979182</v>
       </c>
       <c r="N27" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10095,7 +10095,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M29" t="n">
         <v>449.5135334928325</v>
@@ -10174,22 +10174,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>229.6093331288462</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>225.3066397049837</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10411,22 +10411,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>344.8675110930055</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>309.6353666274674</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L35" t="n">
-        <v>409.3881541004826</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10648,22 +10648,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>248.755351829179</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>152.5681426542525</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,16 +10803,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N38" t="n">
-        <v>437.3469244119842</v>
+        <v>339.6742254965835</v>
       </c>
       <c r="O38" t="n">
         <v>380.8001812627454</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>249.5274280969312</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>298.07096852103</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.1454125711647</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
-        <v>312.9032497650775</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>179.1516856726524</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>162.501822612777</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22993,13 +22993,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>404.3512268697476</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23023,28 +23023,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U8" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>301.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>369.731100678469</v>
+        <v>369.1047367633955</v>
       </c>
       <c r="Y8" t="n">
         <v>386.2379386560536</v>
@@ -23063,22 +23063,22 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>121.8247743700079</v>
       </c>
       <c r="E9" t="n">
-        <v>157.6450804554009</v>
+        <v>132.0247892607701</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>90.41568307852349</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23151,16 +23151,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.7167873157914</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>132.254763809386</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23178,10 +23178,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R10" t="n">
         <v>177.2933913771695</v>
@@ -23227,19 +23227,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>395.924535096324</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23260,19 +23260,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U11" t="n">
-        <v>251.3456529078365</v>
+        <v>238.7699996381505</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>74.15783415264313</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S12" t="n">
-        <v>145.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T12" t="n">
-        <v>174.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U12" t="n">
-        <v>203.7871734072327</v>
+        <v>204.1216209230018</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23394,13 +23394,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>131.8977236196974</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2.424580076758538</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,13 +23418,13 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R13" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S13" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T13" t="n">
         <v>227.9455894282815</v>
@@ -23464,19 +23464,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>395.924535096324</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23497,19 +23497,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S14" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T14" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3456529078365</v>
+        <v>238.7699996381505</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23543,19 +23543,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S15" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>203.375029596744</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2.424580076758538</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,16 +23652,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S16" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T16" t="n">
         <v>227.9455894282815</v>
@@ -23701,19 +23701,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>394.162935096324</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>387.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>311.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>182.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>149.8691179411497</v>
+        <v>122.2790926808335</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>181.4300443259292</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>195.5058243038152</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>237.0350578730948</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23816,25 +23816,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>143.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>172.1647286948216</v>
+        <v>175.8634344455351</v>
       </c>
       <c r="U18" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
-        <v>208.1381871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>205.7729852034775</v>
+        <v>178.1829599431613</v>
       </c>
       <c r="Y18" t="n">
         <v>205.6826957773044</v>
@@ -23850,7 +23850,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C19" t="n">
-        <v>167.2468210986278</v>
+        <v>139.6567958383117</v>
       </c>
       <c r="D19" t="n">
         <v>148.6154730182124</v>
@@ -23859,7 +23859,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F19" t="n">
-        <v>145.4210480229312</v>
+        <v>125.6937293975284</v>
       </c>
       <c r="G19" t="n">
         <v>167.9909793584588</v>
@@ -23889,10 +23889,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169439</v>
+        <v>58.57201799137825</v>
       </c>
       <c r="R19" t="n">
         <v>177.2933913771695</v>
@@ -23904,19 +23904,19 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>224.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>258.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>203.687187762851</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
-        <v>218.5846533520948</v>
+        <v>190.9946280917787</v>
       </c>
     </row>
     <row r="20">
@@ -23926,10 +23926,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>180.4517408780253</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C20" t="n">
-        <v>365.2728917710076</v>
+        <v>152.9875061275654</v>
       </c>
       <c r="D20" t="n">
         <v>354.683041620683</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
@@ -23983,19 +23983,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24023,7 +24023,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -24059,7 +24059,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>76.82817876295805</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -24068,10 +24068,10 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>170.4068831286992</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -24111,7 +24111,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24126,19 +24126,19 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>177.2933913771695</v>
+        <v>155.2593996044852</v>
       </c>
       <c r="S22" t="n">
         <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
         <v>286.3190293564909</v>
@@ -24163,22 +24163,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>153.0000917710075</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>113.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E23" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>203.0173518716929</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24242,31 +24242,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>47.97917063292574</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>133.5693512690413</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,7 +24290,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
         <v>171.6831711038378</v>
@@ -24302,7 +24302,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
         <v>251.6949831609196</v>
@@ -24311,7 +24311,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -24342,7 +24342,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I25" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J25" t="n">
         <v>93.35918011667277</v>
@@ -24390,7 +24390,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="26">
@@ -24412,13 +24412,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>127.2020021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
@@ -24457,19 +24457,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>39.0602672643945</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W26" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X26" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y26" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24479,22 +24479,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>87.67541952728971</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>10.73481636034538</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
@@ -24503,7 +24503,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24527,19 +24527,19 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
         <v>251.6949831609196</v>
@@ -24548,7 +24548,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C28" t="n">
         <v>167.2468210986278</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24655,7 +24655,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
@@ -24694,19 +24694,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>39.07285290783653</v>
+        <v>39.0602672643945</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
@@ -24737,10 +24737,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>7.449670454516252</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24770,19 +24770,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
-        <v>101.4580338610492</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -24837,13 +24837,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>177.2933913771695</v>
+        <v>46.82786452690794</v>
       </c>
       <c r="S31" t="n">
         <v>224.0165980369723</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>211.3294292201823</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>169.5126347727465</v>
       </c>
       <c r="X32" t="n">
-        <v>369.731100678469</v>
+        <v>154.3371029954408</v>
       </c>
       <c r="Y32" t="n">
-        <v>386.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="33">
@@ -24974,7 +24974,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>80.51001400175082</v>
       </c>
       <c r="J33" t="n">
         <v>0.7465913262578567</v>
@@ -25001,28 +25001,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>67.6337339513025</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>179.8319801819373</v>
+        <v>46.6450125965693</v>
       </c>
       <c r="C34" t="n">
         <v>167.2468210986278</v>
       </c>
       <c r="D34" t="n">
-        <v>15.42850543284433</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E34" t="n">
         <v>146.4339626465692</v>
@@ -25114,10 +25114,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>150.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D35" t="n">
-        <v>139.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25129,7 +25129,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>124.0808044327389</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25165,16 +25165,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>33.37681640492011</v>
       </c>
       <c r="U35" t="n">
-        <v>71.96435212238131</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>134.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
@@ -25190,16 +25190,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>134.8062641052684</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
@@ -25241,22 +25241,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>137.1947804961117</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25320,10 +25320,10 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T37" t="n">
-        <v>94.75862184291344</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
         <v>286.3190293564909</v>
@@ -25348,16 +25348,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>167.7338416634806</v>
+        <v>167.3398439804523</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D38" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>202.5490692868066</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
@@ -25369,7 +25369,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>210.4758895704059</v>
+        <v>180.6166735668892</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -25396,7 +25396,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>209.0200695862453</v>
@@ -25405,7 +25405,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>35.95165522480826</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25430,7 +25430,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>10.16911376591386</v>
       </c>
       <c r="D39" t="n">
         <v>147.4450655646388</v>
@@ -25442,16 +25442,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>92.99526603278107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,22 +25475,22 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
@@ -25563,13 +25563,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>153.3360307512229</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25585,16 +25585,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>152.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
-        <v>141.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>195.3452667198258</v>
+        <v>9.67158594678844</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3456529078365</v>
+        <v>68.94806669712813</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25667,28 +25667,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>86.87451113938849</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,7 +25712,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>77.23096333293786</v>
       </c>
       <c r="S42" t="n">
         <v>171.6831711038378</v>
@@ -25721,16 +25721,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>12.5171184636319</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -25797,10 +25797,10 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U43" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060302</v>
+        <v>351669.2246312143</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.61581059</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845365</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.422826439</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>48378.33248915087</v>
+      </c>
+      <c r="C2" t="n">
         <v>48378.33248915088</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
+        <v>51644.51686548872</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51644.51686548873</v>
+      </c>
+      <c r="F2" t="n">
+        <v>51644.51686548873</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51885.6233062447</v>
+      </c>
+      <c r="H2" t="n">
+        <v>74772.30263909959</v>
+      </c>
+      <c r="I2" t="n">
+        <v>74772.30263909959</v>
+      </c>
+      <c r="J2" t="n">
+        <v>74772.30263909958</v>
+      </c>
+      <c r="K2" t="n">
+        <v>74772.30263909958</v>
+      </c>
+      <c r="L2" t="n">
+        <v>72043.0252835296</v>
+      </c>
+      <c r="M2" t="n">
+        <v>72043.02528352961</v>
+      </c>
+      <c r="N2" t="n">
+        <v>72043.0252835296</v>
+      </c>
+      <c r="O2" t="n">
+        <v>71833.1935317696</v>
+      </c>
+      <c r="P2" t="n">
         <v>48378.33248915087</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51690.99534204104</v>
-      </c>
-      <c r="E2" t="n">
-        <v>51690.99534204104</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51690.99534204104</v>
-      </c>
-      <c r="G2" t="n">
-        <v>51933.63669433229</v>
-      </c>
-      <c r="H2" t="n">
-        <v>74770.78047411183</v>
-      </c>
-      <c r="I2" t="n">
-        <v>74770.78047411186</v>
-      </c>
-      <c r="J2" t="n">
-        <v>74770.78047411187</v>
-      </c>
-      <c r="K2" t="n">
-        <v>74770.78047411187</v>
-      </c>
-      <c r="L2" t="n">
-        <v>72001.05351411189</v>
-      </c>
-      <c r="M2" t="n">
-        <v>72001.05351411187</v>
-      </c>
-      <c r="N2" t="n">
-        <v>72001.05351411187</v>
-      </c>
-      <c r="O2" t="n">
-        <v>71787.99759411188</v>
-      </c>
-      <c r="P2" t="n">
-        <v>48378.33248915088</v>
       </c>
     </row>
     <row r="3">
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>7958.431053788175</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26371,40 +26371,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804715</v>
       </c>
       <c r="E4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1832752112465</v>
+        <v>23.85668684891895</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>159.5405981880675</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>14750.73248915087</v>
       </c>
       <c r="C6" t="n">
         <v>14750.73248915088</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860376</v>
+        <v>8478.55543273894</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.66251986037</v>
+        <v>50064.58648652713</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986037</v>
+        <v>50064.58648652713</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912105</v>
+        <v>49644.4185221752</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215214</v>
+        <v>2355.314235302274</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763395</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021526</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021526</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.37112779103</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.37112779102</v>
+        <v>58786.10234497164</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.37112779102</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991223</v>
+        <v>58697.4577056471</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915088</v>
+        <v>48378.33248915087</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,19 +26950,19 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -26971,22 +26971,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,22 +35088,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35170,22 +35170,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,13 +35249,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
         <v>24.58512791403967</v>
@@ -35325,19 +35325,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O11" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35404,25 +35404,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463084</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949496</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>26.86868686868686</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,22 +35878,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N18" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36045,7 +36045,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N20" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O20" t="n">
         <v>150.7019698410586</v>
@@ -36121,13 +36121,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>43.25734905099405</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>239.9766607390412</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36522,7 +36522,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O26" t="n">
-        <v>150.7019698410586</v>
+        <v>150.7019698410587</v>
       </c>
       <c r="P26" t="n">
         <v>90.5657124162131</v>
@@ -36592,22 +36592,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="N27" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36750,7 +36750,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
         <v>219.1673002655598</v>
@@ -36829,22 +36829,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>91.05495334897203</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.216788660003122</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -37066,22 +37066,22 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>206.3131313131313</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>167.5013327054491</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L35" t="n">
-        <v>173.6217391304953</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37236,7 +37236,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37303,22 +37303,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>110.2009720493048</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>9.971898209808115</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,16 +37458,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N38" t="n">
-        <v>207.9338608153932</v>
+        <v>110.2611618999926</v>
       </c>
       <c r="O38" t="n">
         <v>150.7019698410586</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>110.973048317057</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>166.7292564376967</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>104.0555615261842</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
-        <v>77.13683479509021</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>37.01765175063407</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>19.90557816833255</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
